--- a/kopruq_data/menü.xlsx
+++ b/kopruq_data/menü.xlsx
@@ -5,22 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\SPANOVA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\KOPRUQ\kopruq_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA73644-3A14-4B6F-B1BB-F32C91FBD316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1C66C8-E4C2-49B6-9614-9AF45B7775FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{C660A816-C2EF-42B8-A60D-DA7467F2C2B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{C660A816-C2EF-42B8-A60D-DA7467F2C2B7}"/>
   </bookViews>
   <sheets>
     <sheet name="menu" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="superstructure" sheetId="7" r:id="rId3"/>
-    <sheet name="girder" sheetId="4" r:id="rId4"/>
-    <sheet name="pier" sheetId="5" r:id="rId5"/>
-    <sheet name="abutment" sheetId="8" r:id="rId6"/>
-    <sheet name="bearing" sheetId="6" r:id="rId7"/>
-    <sheet name="malzeme" sheetId="9" r:id="rId8"/>
+    <sheet name="girder" sheetId="4" r:id="rId3"/>
+    <sheet name="pier" sheetId="5" r:id="rId4"/>
+    <sheet name="malzeme" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1506,15 +1503,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8169AEDF-63B0-408C-BB3B-673D938535BC}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC332BED-0CB0-4D4B-941A-8E70541A7DCD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1524,7 +1512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05063CB-084C-4E2B-A138-EF188898A3F1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1534,25 +1522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8A318F-EFBA-4A09-A699-F025F2286F36}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5A792F-7FF8-45B0-A1CA-4A02E6F14149}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B8126EA-B602-4AF1-BC4A-C3EE084C4DBF}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>

--- a/kopruq_data/menü.xlsx
+++ b/kopruq_data/menü.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\KOPRUQ\kopruq_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244A2649-6A5F-4CDA-859D-BE6B5385FDD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAFDFC5-1FF3-435D-8AE4-7AF60C338851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C21FCA9D-21B8-4F97-A11C-AED111931456}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{C21FCA9D-21B8-4F97-A11C-AED111931456}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="11" r:id="rId1"/>
@@ -80,7 +80,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -257,17 +257,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>77</xdr:col>
-      <xdr:colOff>273178</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>248809</xdr:rowOff>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>260545</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>111580</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFAAFC75-E5AA-99B7-295C-321982682D5C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34485F7A-E6BE-770C-F2D2-3ED79CF232D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -284,7 +284,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="24371428" cy="12495238"/>
+          <a:ext cx="14600000" cy="7904762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/kopruq_data/menü.xlsx
+++ b/kopruq_data/menü.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\KOPRUQ\kopruq_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAFDFC5-1FF3-435D-8AE4-7AF60C338851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB427BC-D506-43D7-B359-7DA46B1C86D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{C21FCA9D-21B8-4F97-A11C-AED111931456}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{C21FCA9D-21B8-4F97-A11C-AED111931456}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="11" r:id="rId1"/>
@@ -89,6 +89,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0000FF"/>
+      <color rgb="FF00FF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -285,6 +291,740 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="14600000" cy="7904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>283475</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>179808</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB475562-9E82-B44A-02C1-FF4BDBDD9964}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8715375"/>
+          <a:ext cx="18200000" cy="9333333"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>138473</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>67236</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>231322</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D43C34E-5DC9-4C35-0E89-620A7C15502F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1967433" y="9663473"/>
+          <a:ext cx="7175767" cy="3358563"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00FF00"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>115261</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>68035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>92850</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>176892</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="Rectangle 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D81BDBE-F4BE-42A7-8664-A5A5EAA15F86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1993047" y="13130892"/>
+          <a:ext cx="7175767" cy="5279571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="0000FF"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>204108</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>108859</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>244928</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E71A5D15-444E-45D9-926E-B8DEB2E680A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9280072" y="9633859"/>
+          <a:ext cx="8654142" cy="6667498"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>68036</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>57</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>201706</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2EE2386-AD7A-464B-95D0-5E5743C0093D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9266464" y="16396607"/>
+          <a:ext cx="8667750" cy="2038670"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFC000"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="tr-TR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>40821</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>231322</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8AF4533-C8BD-74AA-F996-949BC4D616B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40821" y="9878786"/>
+          <a:ext cx="1578429" cy="421822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1600" b="1"/>
+            <a:t>STRUCTURE</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>163287</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>176894</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>258536</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE9C80A4-F4EE-4059-A644-88CD66554B0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4857751" y="9906000"/>
+          <a:ext cx="1578429" cy="421822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1600" b="1"/>
+            <a:t>PARAMETERS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>122464</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>81643</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{858E9ED8-A5DB-4177-95A6-0B4F48AF8E50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12600214" y="9919607"/>
+          <a:ext cx="2190750" cy="421822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1600" b="1"/>
+            <a:t>CANDIDATE SECTIONS</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>163286</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>136072</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>68036</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>13608</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDA7B04-231E-4AAF-975C-A5BCB747CB61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3918857" y="13471072"/>
+          <a:ext cx="1782536" cy="421822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1600" b="1"/>
+            <a:t>SECTION PREVIEW</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>176892</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>244930</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>40822</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>122466</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E06C1E-A505-4370-87F0-D1810D856874}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12069535" y="16573501"/>
+          <a:ext cx="2367644" cy="421822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="tr-TR" sz="1600" b="1"/>
+            <a:t>SECTION PROPERTIES</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>27213</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>258536</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>56</xdr:col>
+      <xdr:colOff>297982</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Picture 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A95C837E-9C95-30A8-74CC-271A4C050B9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27213" y="18764250"/>
+          <a:ext cx="17796769" cy="9851571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>54</xdr:col>
+      <xdr:colOff>33262</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>115965</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37B73AFC-365D-C276-F2BE-E6D93172D95D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="28942393"/>
+          <a:ext cx="16933333" cy="8457143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/kopruq_data/menü.xlsx
+++ b/kopruq_data/menü.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_ZHarput_Data\KOPRUQ\kopruq_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB427BC-D506-43D7-B359-7DA46B1C86D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86877E5-1292-42E1-ABB3-DB6CAA02B02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{C21FCA9D-21B8-4F97-A11C-AED111931456}"/>
   </bookViews>
@@ -291,740 +291,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="14600000" cy="7904762"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>57</xdr:col>
-      <xdr:colOff>283475</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>179808</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB475562-9E82-B44A-02C1-FF4BDBDD9964}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="8715375"/>
-          <a:ext cx="18200000" cy="9333333"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>89647</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>138473</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>67236</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>231322</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Rectangle 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D43C34E-5DC9-4C35-0E89-620A7C15502F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1967433" y="9663473"/>
-          <a:ext cx="7175767" cy="3358563"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="00FF00"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="tr-TR" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>115261</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>68035</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>92850</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>176892</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Rectangle 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D81BDBE-F4BE-42A7-8664-A5A5EAA15F86}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1993047" y="13130892"/>
-          <a:ext cx="7175767" cy="5279571"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0000FF"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="tr-TR" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>204108</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>108859</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>57</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>244928</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Rectangle 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E71A5D15-444E-45D9-926E-B8DEB2E680A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9280072" y="9633859"/>
-          <a:ext cx="8654142" cy="6667498"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="tr-TR" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>68036</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>57</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>201706</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Rectangle 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2EE2386-AD7A-464B-95D0-5E5743C0093D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9266464" y="16396607"/>
-          <a:ext cx="8667750" cy="2038670"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFC000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="tr-TR" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>40821</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>81643</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>54429</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>231322</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="TextBox 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8AF4533-C8BD-74AA-F996-949BC4D616B2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="40821" y="9878786"/>
-          <a:ext cx="1578429" cy="421822"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="1600" b="1"/>
-            <a:t>STRUCTURE</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>163287</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>176894</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>258536</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="TextBox 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE9C80A4-F4EE-4059-A644-88CD66554B0B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4857751" y="9906000"/>
-          <a:ext cx="1578429" cy="421822"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="1600" b="1"/>
-            <a:t>PARAMETERS</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>81643</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>122464</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>81643</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="TextBox 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{858E9ED8-A5DB-4177-95A6-0B4F48AF8E50}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12600214" y="9919607"/>
-          <a:ext cx="2190750" cy="421822"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="1600" b="1"/>
-            <a:t>CANDIDATE SECTIONS</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>163286</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>68036</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>13608</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="TextBox 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BDA7B04-231E-4AAF-975C-A5BCB747CB61}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3918857" y="13471072"/>
-          <a:ext cx="1782536" cy="421822"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="1600" b="1"/>
-            <a:t>SECTION PREVIEW</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>176892</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>244930</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>40822</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>122466</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="TextBox 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04E06C1E-A505-4370-87F0-D1810D856874}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12069535" y="16573501"/>
-          <a:ext cx="2367644" cy="421822"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="tr-TR" sz="1600" b="1"/>
-            <a:t>SECTION PROPERTIES</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>27213</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>258536</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>56</xdr:col>
-      <xdr:colOff>297982</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>40821</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="Picture 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A95C837E-9C95-30A8-74CC-271A4C050B9A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27213" y="18764250"/>
-          <a:ext cx="17796769" cy="9851571"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>54</xdr:col>
-      <xdr:colOff>33262</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>115965</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37B73AFC-365D-C276-F2BE-E6D93172D95D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="28942393"/>
-          <a:ext cx="16933333" cy="8457143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
